--- a/粤徽交付中心八月数据看板.xlsx
+++ b/粤徽交付中心八月数据看板.xlsx
@@ -1139,34 +1139,34 @@
       </c>
       <c r="F2" s="11">
         <f>=SUMIFS(F:F,A:A,B2,B:B,C2)</f>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G2" s="12">
         <f>=SUM(G8:G14)</f>
-        <v>1239</v>
+        <v>1392</v>
       </c>
       <c r="H2" s="12">
         <f>=SUM(H8:H14)</f>
-        <v>258</v>
+        <v>291</v>
       </c>
       <c r="I2" s="12">
         <f>=SUM(I8:I14)</f>
-        <v>139</v>
+        <v>158</v>
       </c>
       <c r="J2" s="12">
         <f>=SUM(J8:J14)</f>
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="K2" s="12">
         <f>=SUM(K8:K14)</f>
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="L2" s="13">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="M2" s="14">
         <f>=K2/L2</f>
-        <v>0.233333333333333</v>
+        <v>0.385714285714286</v>
       </c>
       <c r="N2" s="4" t="s"/>
       <c r="O2" s="4" t="s"/>
@@ -1343,34 +1343,34 @@
       </c>
       <c r="F3" s="11">
         <f>=SUMIFS(F:F,A:A,B3,B:B,C3)</f>
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G3" s="12">
         <f>=SUM(G15:G23)</f>
-        <v>4011</v>
+        <v>4267</v>
       </c>
       <c r="H3" s="12">
         <f>=SUM(H15:H23)</f>
-        <v>407</v>
+        <v>457</v>
       </c>
       <c r="I3" s="12">
         <f>=SUM(I15:I23)</f>
-        <v>221</v>
+        <v>251</v>
       </c>
       <c r="J3" s="12">
         <f>=SUM(J15:J23)</f>
-        <v>99</v>
+        <v>117</v>
       </c>
       <c r="K3" s="12">
         <f>=SUM(K15:K23)</f>
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L3" s="13">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="M3" s="14">
         <f>=K3/L3</f>
-        <v>0.325</v>
+        <v>0.5</v>
       </c>
       <c r="N3" s="4" t="s"/>
       <c r="O3" s="4" t="s"/>
@@ -1542,35 +1542,35 @@
       </c>
       <c r="F4" s="16">
         <f>=SUM(F2:F3)</f>
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G4" s="16">
         <f>=SUM(G2:G3)</f>
-        <v>5250</v>
+        <v>5659</v>
       </c>
       <c r="H4" s="16">
         <f>=SUM(H2:H3)</f>
-        <v>665</v>
+        <v>748</v>
       </c>
       <c r="I4" s="16">
         <f>=SUM(I2:I3)</f>
-        <v>360</v>
+        <v>409</v>
       </c>
       <c r="J4" s="16">
         <f>=SUM(J2:J3)</f>
-        <v>155</v>
+        <v>181</v>
       </c>
       <c r="K4" s="16">
         <f>=SUM(K2:K3)</f>
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="L4" s="18">
         <f>=SUM(L2:L3)</f>
-        <v>210</v>
+        <v>160</v>
       </c>
       <c r="M4" s="19">
         <f>=K4/L4</f>
-        <v>0.285714285714286</v>
+        <v>0.45</v>
       </c>
       <c r="N4" s="4" t="s"/>
       <c r="O4" s="4" t="s"/>
@@ -1907,7 +1907,7 @@
         <v>20</v>
       </c>
       <c r="F6" s="22">
-        <v>46261</v>
+        <v>46265</v>
       </c>
       <c r="G6" s="23" t="s">
         <v>21</v>
@@ -2659,7 +2659,7 @@
         <v>25</v>
       </c>
       <c r="F8" s="39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G8" s="40">
         <f>=SUMIF($N$7:$FH$7,"新增微信",N8:FH8)</f>
@@ -2682,11 +2682,11 @@
         <v>1</v>
       </c>
       <c r="L8" s="41">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="M8" s="42">
         <f>=K8/L8</f>
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="N8" s="37">
         <v>0</v>
@@ -2891,34 +2891,34 @@
         <v>27</v>
       </c>
       <c r="F9" s="39">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G9" s="40">
         <f>=SUMIF($N$7:$FH$7,"新增微信",N9:FH9)</f>
-        <v>354</v>
+        <v>391</v>
       </c>
       <c r="H9" s="40">
         <f>=SUMIF($O$7:$FI$7,"预约",O9:FI9)</f>
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="I9" s="40">
         <f>=SUMIF($P$7:$FJ$7,"到场",P9:FJ9)</f>
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="J9" s="40">
         <f>=SUMIF($Q$7:$FK$7,"合格",Q9:FK9)</f>
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="K9" s="40">
         <f>=SUMIF($R$7:$FL$7,"在职",R9:FL9)</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L9" s="41">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="M9" s="42">
         <f>=K9/L9</f>
-        <v>0.233333333333333</v>
+        <v>0.45</v>
       </c>
       <c r="N9" s="37">
         <v>3</v>
@@ -3323,28 +3323,68 @@
         <v>5</v>
       </c>
       <c r="ER9" s="45">
-        <v>1</v>
-      </c>
-      <c r="ES9" s="44" t="s"/>
-      <c r="ET9" s="44" t="s"/>
-      <c r="EU9" s="44" t="s"/>
-      <c r="EV9" s="44" t="s"/>
-      <c r="EW9" s="44" t="s"/>
-      <c r="EX9" s="45" t="s"/>
-      <c r="EY9" s="45" t="s"/>
-      <c r="EZ9" s="45" t="s"/>
-      <c r="FA9" s="45" t="s"/>
-      <c r="FB9" s="45" t="s"/>
-      <c r="FC9" s="44" t="s"/>
-      <c r="FD9" s="44" t="s"/>
-      <c r="FE9" s="44" t="s"/>
-      <c r="FF9" s="44" t="s"/>
-      <c r="FG9" s="44" t="s"/>
-      <c r="FH9" s="45" t="s"/>
-      <c r="FI9" s="45" t="s"/>
-      <c r="FJ9" s="45" t="s"/>
-      <c r="FK9" s="45" t="s"/>
-      <c r="FL9" s="45" t="s"/>
+        <v>0</v>
+      </c>
+      <c r="ES9" s="44">
+        <v>17</v>
+      </c>
+      <c r="ET9" s="44">
+        <v>3</v>
+      </c>
+      <c r="EU9" s="44">
+        <v>3</v>
+      </c>
+      <c r="EV9" s="44">
+        <v>2</v>
+      </c>
+      <c r="EW9" s="44">
+        <v>3</v>
+      </c>
+      <c r="EX9" s="45">
+        <v>2</v>
+      </c>
+      <c r="EY9" s="45">
+        <v>2</v>
+      </c>
+      <c r="EZ9" s="45">
+        <v>1</v>
+      </c>
+      <c r="FA9" s="45">
+        <v>0</v>
+      </c>
+      <c r="FB9" s="45">
+        <v>0</v>
+      </c>
+      <c r="FC9" s="44">
+        <v>10</v>
+      </c>
+      <c r="FD9" s="44">
+        <v>1</v>
+      </c>
+      <c r="FE9" s="44">
+        <v>1</v>
+      </c>
+      <c r="FF9" s="44">
+        <v>1</v>
+      </c>
+      <c r="FG9" s="44">
+        <v>0</v>
+      </c>
+      <c r="FH9" s="45">
+        <v>8</v>
+      </c>
+      <c r="FI9" s="45">
+        <v>4</v>
+      </c>
+      <c r="FJ9" s="45">
+        <v>3</v>
+      </c>
+      <c r="FK9" s="45">
+        <v>3</v>
+      </c>
+      <c r="FL9" s="45">
+        <v>0</v>
+      </c>
     </row>
     <row r="10" spans="1:168">
       <c r="A10" s="37" t="s">
@@ -3367,30 +3407,30 @@
       </c>
       <c r="G10" s="40">
         <f>=SUMIF($N$7:$FH$7,"新增微信",N10:FH10)</f>
-        <v>529</v>
+        <v>599</v>
       </c>
       <c r="H10" s="40">
         <f>=SUMIF($O$7:$FI$7,"预约",O10:FI10)</f>
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="I10" s="40">
         <f>=SUMIF($P$7:$FJ$7,"到场",P10:FJ10)</f>
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="J10" s="40">
         <f>=SUMIF($Q$7:$FK$7,"合格",Q10:FK10)</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K10" s="40">
         <f>=SUMIF($R$7:$FL$7,"在职",R10:FL10)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L10" s="41">
         <v>20</v>
       </c>
       <c r="M10" s="42">
         <f>=K10/L10</f>
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="N10" s="37">
         <v>4</v>
@@ -3797,26 +3837,66 @@
       <c r="ER10" s="45">
         <v>0</v>
       </c>
-      <c r="ES10" s="44" t="s"/>
-      <c r="ET10" s="44" t="s"/>
-      <c r="EU10" s="44" t="s"/>
-      <c r="EV10" s="44" t="s"/>
-      <c r="EW10" s="44" t="s"/>
-      <c r="EX10" s="45" t="s"/>
-      <c r="EY10" s="45" t="s"/>
-      <c r="EZ10" s="45" t="s"/>
-      <c r="FA10" s="45" t="s"/>
-      <c r="FB10" s="45" t="s"/>
-      <c r="FC10" s="44" t="s"/>
-      <c r="FD10" s="44" t="s"/>
-      <c r="FE10" s="44" t="s"/>
-      <c r="FF10" s="44" t="s"/>
-      <c r="FG10" s="44" t="s"/>
-      <c r="FH10" s="45" t="s"/>
-      <c r="FI10" s="45" t="s"/>
-      <c r="FJ10" s="45" t="s"/>
-      <c r="FK10" s="45" t="s"/>
-      <c r="FL10" s="45" t="s"/>
+      <c r="ES10" s="44">
+        <v>27</v>
+      </c>
+      <c r="ET10" s="44">
+        <v>5</v>
+      </c>
+      <c r="EU10" s="44">
+        <v>2</v>
+      </c>
+      <c r="EV10" s="44">
+        <v>1</v>
+      </c>
+      <c r="EW10" s="44">
+        <v>0</v>
+      </c>
+      <c r="EX10" s="45">
+        <v>14</v>
+      </c>
+      <c r="EY10" s="45">
+        <v>3</v>
+      </c>
+      <c r="EZ10" s="45">
+        <v>2</v>
+      </c>
+      <c r="FA10" s="45">
+        <v>0</v>
+      </c>
+      <c r="FB10" s="45">
+        <v>1</v>
+      </c>
+      <c r="FC10" s="44">
+        <v>20</v>
+      </c>
+      <c r="FD10" s="44">
+        <v>0</v>
+      </c>
+      <c r="FE10" s="44">
+        <v>0</v>
+      </c>
+      <c r="FF10" s="44">
+        <v>0</v>
+      </c>
+      <c r="FG10" s="44">
+        <v>0</v>
+      </c>
+      <c r="FH10" s="45">
+        <v>9</v>
+      </c>
+      <c r="FI10" s="45">
+        <v>7</v>
+      </c>
+      <c r="FJ10" s="45">
+        <v>4</v>
+      </c>
+      <c r="FK10" s="45">
+        <v>0</v>
+      </c>
+      <c r="FL10" s="45">
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="1:168">
       <c r="A11" s="37" t="s">
@@ -3839,30 +3919,30 @@
       </c>
       <c r="G11" s="40">
         <f>=SUMIF($N$7:$FH$7,"新增微信",N11:FH11)</f>
-        <v>341</v>
+        <v>387</v>
       </c>
       <c r="H11" s="40">
         <f>=SUMIF($O$7:$FI$7,"预约",O11:FI11)</f>
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="I11" s="40">
         <f>=SUMIF($P$7:$FJ$7,"到场",P11:FJ11)</f>
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J11" s="40">
         <f>=SUMIF($Q$7:$FK$7,"合格",Q11:FK11)</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K11" s="40">
         <f>=SUMIF($R$7:$FL$7,"在职",R11:FL11)</f>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L11" s="41">
         <v>20</v>
       </c>
       <c r="M11" s="42">
         <f>=K11/L11</f>
-        <v>0.35</v>
+        <v>0.5</v>
       </c>
       <c r="N11" s="37" t="s"/>
       <c r="O11" s="37" t="s"/>
@@ -4219,26 +4299,66 @@
       <c r="ER11" s="45">
         <v>0</v>
       </c>
-      <c r="ES11" s="44" t="s"/>
-      <c r="ET11" s="44" t="s"/>
-      <c r="EU11" s="44" t="s"/>
-      <c r="EV11" s="44" t="s"/>
-      <c r="EW11" s="44" t="s"/>
-      <c r="EX11" s="45" t="s"/>
-      <c r="EY11" s="45" t="s"/>
-      <c r="EZ11" s="45" t="s"/>
-      <c r="FA11" s="45" t="s"/>
-      <c r="FB11" s="45" t="s"/>
-      <c r="FC11" s="44" t="s"/>
-      <c r="FD11" s="44" t="s"/>
-      <c r="FE11" s="44" t="s"/>
-      <c r="FF11" s="44" t="s"/>
-      <c r="FG11" s="44" t="s"/>
-      <c r="FH11" s="45" t="s"/>
-      <c r="FI11" s="45" t="s"/>
-      <c r="FJ11" s="45" t="s"/>
-      <c r="FK11" s="45" t="s"/>
-      <c r="FL11" s="45" t="s"/>
+      <c r="ES11" s="44">
+        <v>9</v>
+      </c>
+      <c r="ET11" s="44">
+        <v>5</v>
+      </c>
+      <c r="EU11" s="44">
+        <v>1</v>
+      </c>
+      <c r="EV11" s="44">
+        <v>1</v>
+      </c>
+      <c r="EW11" s="44">
+        <v>2</v>
+      </c>
+      <c r="EX11" s="45">
+        <v>4</v>
+      </c>
+      <c r="EY11" s="45">
+        <v>1</v>
+      </c>
+      <c r="EZ11" s="45">
+        <v>1</v>
+      </c>
+      <c r="FA11" s="45">
+        <v>0</v>
+      </c>
+      <c r="FB11" s="45">
+        <v>1</v>
+      </c>
+      <c r="FC11" s="44">
+        <v>18</v>
+      </c>
+      <c r="FD11" s="44">
+        <v>0</v>
+      </c>
+      <c r="FE11" s="44">
+        <v>0</v>
+      </c>
+      <c r="FF11" s="44">
+        <v>0</v>
+      </c>
+      <c r="FG11" s="44">
+        <v>0</v>
+      </c>
+      <c r="FH11" s="45">
+        <v>15</v>
+      </c>
+      <c r="FI11" s="45">
+        <v>2</v>
+      </c>
+      <c r="FJ11" s="45">
+        <v>1</v>
+      </c>
+      <c r="FK11" s="45">
+        <v>0</v>
+      </c>
+      <c r="FL11" s="45">
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:168">
       <c r="A12" s="37" t="s"/>
@@ -4966,34 +5086,34 @@
         <v>27</v>
       </c>
       <c r="F16" s="39">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G16" s="40">
         <f>=SUMIF($N$7:$FH$7,"新增微信",N16:FH16)</f>
-        <v>553</v>
+        <v>622</v>
       </c>
       <c r="H16" s="40">
         <f>=SUMIF($O$7:$FI$7,"预约",O16:FI16)</f>
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="I16" s="40">
         <f>=SUMIF($P$7:$FJ$7,"到场",P16:FJ16)</f>
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="J16" s="40">
         <f>=SUMIF($Q$7:$FK$7,"合格",Q16:FK16)</f>
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="K16" s="40">
         <f>=SUMIF($R$7:$FL$7,"在职",R16:FL16)</f>
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="L16" s="41">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="M16" s="42">
         <f>=K16/L16</f>
-        <v>0.425</v>
+        <v>1.05</v>
       </c>
       <c r="N16" s="46">
         <v>13</v>
@@ -5400,26 +5520,66 @@
       <c r="ER16" s="45">
         <v>0</v>
       </c>
-      <c r="ES16" s="44" t="s"/>
-      <c r="ET16" s="44" t="s"/>
-      <c r="EU16" s="44" t="s"/>
-      <c r="EV16" s="44" t="s"/>
-      <c r="EW16" s="44" t="s"/>
-      <c r="EX16" s="45" t="s"/>
-      <c r="EY16" s="45" t="s"/>
-      <c r="EZ16" s="45" t="s"/>
-      <c r="FA16" s="45" t="s"/>
-      <c r="FB16" s="45" t="s"/>
-      <c r="FC16" s="44" t="s"/>
-      <c r="FD16" s="44" t="s"/>
-      <c r="FE16" s="44" t="s"/>
-      <c r="FF16" s="44" t="s"/>
-      <c r="FG16" s="44" t="s"/>
-      <c r="FH16" s="45" t="s"/>
-      <c r="FI16" s="45" t="s"/>
-      <c r="FJ16" s="45" t="s"/>
-      <c r="FK16" s="45" t="s"/>
-      <c r="FL16" s="45" t="s"/>
+      <c r="ES16" s="44">
+        <v>19</v>
+      </c>
+      <c r="ET16" s="44">
+        <v>5</v>
+      </c>
+      <c r="EU16" s="44">
+        <v>5</v>
+      </c>
+      <c r="EV16" s="44">
+        <v>1</v>
+      </c>
+      <c r="EW16" s="44">
+        <v>2</v>
+      </c>
+      <c r="EX16" s="45">
+        <v>7</v>
+      </c>
+      <c r="EY16" s="45">
+        <v>0</v>
+      </c>
+      <c r="EZ16" s="45">
+        <v>0</v>
+      </c>
+      <c r="FA16" s="45">
+        <v>0</v>
+      </c>
+      <c r="FB16" s="45">
+        <v>2</v>
+      </c>
+      <c r="FC16" s="44">
+        <v>24</v>
+      </c>
+      <c r="FD16" s="44">
+        <v>1</v>
+      </c>
+      <c r="FE16" s="44">
+        <v>1</v>
+      </c>
+      <c r="FF16" s="44">
+        <v>0</v>
+      </c>
+      <c r="FG16" s="44">
+        <v>0</v>
+      </c>
+      <c r="FH16" s="45">
+        <v>19</v>
+      </c>
+      <c r="FI16" s="45">
+        <v>6</v>
+      </c>
+      <c r="FJ16" s="45">
+        <v>4</v>
+      </c>
+      <c r="FK16" s="45">
+        <v>4</v>
+      </c>
+      <c r="FL16" s="45">
+        <v>0</v>
+      </c>
     </row>
     <row r="17" spans="1:168">
       <c r="A17" s="37" t="s">
@@ -5442,15 +5602,15 @@
       </c>
       <c r="G17" s="40">
         <f>=SUMIF($N$7:$FH$7,"新增微信",N17:FH17)</f>
-        <v>1632</v>
+        <v>1653</v>
       </c>
       <c r="H17" s="40">
         <f>=SUMIF($O$7:$FI$7,"预约",O17:FI17)</f>
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I17" s="40">
         <f>=SUMIF($P$7:$FJ$7,"到场",P17:FJ17)</f>
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J17" s="40">
         <f>=SUMIF($Q$7:$FK$7,"合格",Q17:FK17)</f>
@@ -5660,7 +5820,7 @@
         <v>0</v>
       </c>
       <c r="BZ17" s="47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CA17" s="44">
         <v>3</v>
@@ -5872,26 +6032,66 @@
       <c r="ER17" s="45">
         <v>0</v>
       </c>
-      <c r="ES17" s="44" t="s"/>
-      <c r="ET17" s="44" t="s"/>
-      <c r="EU17" s="44" t="s"/>
-      <c r="EV17" s="44" t="s"/>
-      <c r="EW17" s="44" t="s"/>
-      <c r="EX17" s="45" t="s"/>
-      <c r="EY17" s="45" t="s"/>
-      <c r="EZ17" s="45" t="s"/>
-      <c r="FA17" s="45" t="s"/>
-      <c r="FB17" s="45" t="s"/>
-      <c r="FC17" s="44" t="s"/>
-      <c r="FD17" s="44" t="s"/>
-      <c r="FE17" s="44" t="s"/>
-      <c r="FF17" s="44" t="s"/>
-      <c r="FG17" s="44" t="s"/>
-      <c r="FH17" s="45" t="s"/>
-      <c r="FI17" s="45" t="s"/>
-      <c r="FJ17" s="45" t="s"/>
-      <c r="FK17" s="45" t="s"/>
-      <c r="FL17" s="45" t="s"/>
+      <c r="ES17" s="44">
+        <v>6</v>
+      </c>
+      <c r="ET17" s="44">
+        <v>1</v>
+      </c>
+      <c r="EU17" s="44">
+        <v>1</v>
+      </c>
+      <c r="EV17" s="44">
+        <v>0</v>
+      </c>
+      <c r="EW17" s="44">
+        <v>1</v>
+      </c>
+      <c r="EX17" s="45">
+        <v>2</v>
+      </c>
+      <c r="EY17" s="45">
+        <v>5</v>
+      </c>
+      <c r="EZ17" s="45">
+        <v>2</v>
+      </c>
+      <c r="FA17" s="45">
+        <v>0</v>
+      </c>
+      <c r="FB17" s="45">
+        <v>0</v>
+      </c>
+      <c r="FC17" s="44">
+        <v>9</v>
+      </c>
+      <c r="FD17" s="44">
+        <v>1</v>
+      </c>
+      <c r="FE17" s="44">
+        <v>0</v>
+      </c>
+      <c r="FF17" s="44">
+        <v>0</v>
+      </c>
+      <c r="FG17" s="44">
+        <v>0</v>
+      </c>
+      <c r="FH17" s="45">
+        <v>4</v>
+      </c>
+      <c r="FI17" s="45">
+        <v>2</v>
+      </c>
+      <c r="FJ17" s="45">
+        <v>0</v>
+      </c>
+      <c r="FK17" s="45">
+        <v>0</v>
+      </c>
+      <c r="FL17" s="45">
+        <v>0</v>
+      </c>
     </row>
     <row r="18" spans="1:168">
       <c r="A18" s="37" t="s">
@@ -5914,30 +6114,30 @@
       </c>
       <c r="G18" s="50">
         <f>=SUMIF($N$7:$FH$7,"新增微信",N18:FH18)</f>
-        <v>504</v>
+        <v>543</v>
       </c>
       <c r="H18" s="50">
         <f>=SUMIF($O$7:$FI$7,"预约",O18:FI18)</f>
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="I18" s="50">
         <f>=SUMIF($P$7:$FJ$7,"到场",P18:FJ18)</f>
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="J18" s="50">
         <f>=SUMIF($Q$7:$FK$7,"合格",Q18:FK18)</f>
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="K18" s="50">
         <f>=SUMIF($R$7:$FL$7,"在职",R18:FL18)</f>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="L18" s="51">
         <v>20</v>
       </c>
       <c r="M18" s="52">
         <f>=K18/L18</f>
-        <v>0.4</v>
+        <v>0.55</v>
       </c>
       <c r="N18" s="53">
         <v>11</v>
@@ -6344,26 +6544,66 @@
       <c r="ER18" s="45">
         <v>0</v>
       </c>
-      <c r="ES18" s="54" t="s"/>
-      <c r="ET18" s="54" t="s"/>
-      <c r="EU18" s="54" t="s"/>
-      <c r="EV18" s="54" t="s"/>
-      <c r="EW18" s="54" t="s"/>
-      <c r="EX18" s="45" t="s"/>
-      <c r="EY18" s="45" t="s"/>
-      <c r="EZ18" s="45" t="s"/>
-      <c r="FA18" s="45" t="s"/>
-      <c r="FB18" s="45" t="s"/>
-      <c r="FC18" s="54" t="s"/>
-      <c r="FD18" s="54" t="s"/>
-      <c r="FE18" s="54" t="s"/>
-      <c r="FF18" s="54" t="s"/>
-      <c r="FG18" s="54" t="s"/>
-      <c r="FH18" s="45" t="s"/>
-      <c r="FI18" s="45" t="s"/>
-      <c r="FJ18" s="45" t="s"/>
-      <c r="FK18" s="45" t="s"/>
-      <c r="FL18" s="45" t="s"/>
+      <c r="ES18" s="54">
+        <v>12</v>
+      </c>
+      <c r="ET18" s="54">
+        <v>2</v>
+      </c>
+      <c r="EU18" s="54">
+        <v>2</v>
+      </c>
+      <c r="EV18" s="54">
+        <v>2</v>
+      </c>
+      <c r="EW18" s="54">
+        <v>0</v>
+      </c>
+      <c r="EX18" s="45">
+        <v>12</v>
+      </c>
+      <c r="EY18" s="45">
+        <v>1</v>
+      </c>
+      <c r="EZ18" s="45">
+        <v>0</v>
+      </c>
+      <c r="FA18" s="45">
+        <v>0</v>
+      </c>
+      <c r="FB18" s="45">
+        <v>2</v>
+      </c>
+      <c r="FC18" s="54">
+        <v>5</v>
+      </c>
+      <c r="FD18" s="54">
+        <v>4</v>
+      </c>
+      <c r="FE18" s="54">
+        <v>2</v>
+      </c>
+      <c r="FF18" s="54">
+        <v>2</v>
+      </c>
+      <c r="FG18" s="54">
+        <v>0</v>
+      </c>
+      <c r="FH18" s="45">
+        <v>10</v>
+      </c>
+      <c r="FI18" s="45">
+        <v>5</v>
+      </c>
+      <c r="FJ18" s="45">
+        <v>4</v>
+      </c>
+      <c r="FK18" s="45">
+        <v>3</v>
+      </c>
+      <c r="FL18" s="45">
+        <v>1</v>
+      </c>
     </row>
     <row r="19" spans="1:168">
       <c r="A19" s="37" t="s">
@@ -6382,34 +6622,34 @@
         <v>27</v>
       </c>
       <c r="F19" s="39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G19" s="40">
         <f>=SUMIF($N$7:$FH$7,"新增微信",N19:FH19)</f>
-        <v>263</v>
+        <v>290</v>
       </c>
       <c r="H19" s="40">
         <f>=SUMIF($O$7:$FI$7,"预约",O19:FI19)</f>
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="I19" s="40">
         <f>=SUMIF($P$7:$FJ$7,"到场",P19:FJ19)</f>
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J19" s="40">
         <f>=SUMIF($Q$7:$FK$7,"合格",Q19:FK19)</f>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K19" s="40">
         <f>=SUMIF($R$7:$FL$7,"在职",R19:FL19)</f>
         <v>1</v>
       </c>
       <c r="L19" s="41">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="M19" s="42">
         <f>=K19/L19</f>
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="N19" s="46" t="s"/>
       <c r="O19" s="46" t="s"/>
@@ -6796,26 +7036,66 @@
       <c r="ER19" s="45">
         <v>0</v>
       </c>
-      <c r="ES19" s="44" t="s"/>
-      <c r="ET19" s="44" t="s"/>
-      <c r="EU19" s="44" t="s"/>
-      <c r="EV19" s="44" t="s"/>
-      <c r="EW19" s="44" t="s"/>
-      <c r="EX19" s="45" t="s"/>
-      <c r="EY19" s="45" t="s"/>
-      <c r="EZ19" s="45" t="s"/>
-      <c r="FA19" s="45" t="s"/>
-      <c r="FB19" s="45" t="s"/>
-      <c r="FC19" s="44" t="s"/>
-      <c r="FD19" s="44" t="s"/>
-      <c r="FE19" s="44" t="s"/>
-      <c r="FF19" s="44" t="s"/>
-      <c r="FG19" s="44" t="s"/>
-      <c r="FH19" s="45" t="s"/>
-      <c r="FI19" s="45" t="s"/>
-      <c r="FJ19" s="45" t="s"/>
-      <c r="FK19" s="45" t="s"/>
-      <c r="FL19" s="45" t="s"/>
+      <c r="ES19" s="44">
+        <v>14</v>
+      </c>
+      <c r="ET19" s="44">
+        <v>0</v>
+      </c>
+      <c r="EU19" s="44">
+        <v>0</v>
+      </c>
+      <c r="EV19" s="44">
+        <v>0</v>
+      </c>
+      <c r="EW19" s="44">
+        <v>0</v>
+      </c>
+      <c r="EX19" s="45">
+        <v>3</v>
+      </c>
+      <c r="EY19" s="45">
+        <v>2</v>
+      </c>
+      <c r="EZ19" s="45">
+        <v>2</v>
+      </c>
+      <c r="FA19" s="45">
+        <v>2</v>
+      </c>
+      <c r="FB19" s="45">
+        <v>0</v>
+      </c>
+      <c r="FC19" s="44">
+        <v>3</v>
+      </c>
+      <c r="FD19" s="44">
+        <v>2</v>
+      </c>
+      <c r="FE19" s="44">
+        <v>0</v>
+      </c>
+      <c r="FF19" s="44">
+        <v>0</v>
+      </c>
+      <c r="FG19" s="44">
+        <v>0</v>
+      </c>
+      <c r="FH19" s="45">
+        <v>7</v>
+      </c>
+      <c r="FI19" s="45">
+        <v>3</v>
+      </c>
+      <c r="FJ19" s="45">
+        <v>3</v>
+      </c>
+      <c r="FK19" s="45">
+        <v>1</v>
+      </c>
+      <c r="FL19" s="45">
+        <v>0</v>
+      </c>
     </row>
     <row r="20" spans="1:168">
       <c r="A20" s="37" t="s">
@@ -6838,30 +7118,30 @@
       </c>
       <c r="G20" s="40">
         <f>=SUMIF($N$7:$FH$7,"新增微信",N20:FH20)</f>
-        <v>1059</v>
+        <v>1159</v>
       </c>
       <c r="H20" s="40">
         <f>=SUMIF($O$7:$FI$7,"预约",O20:FI20)</f>
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="I20" s="40">
         <f>=SUMIF($P$7:$FJ$7,"到场",P20:FJ20)</f>
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="J20" s="40">
         <f>=SUMIF($Q$7:$FK$7,"合格",Q20:FK20)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K20" s="40">
         <f>=SUMIF($R$7:$FL$7,"在职",R20:FL20)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L20" s="41">
         <v>20</v>
       </c>
       <c r="M20" s="42">
         <f>=K20/L20</f>
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="N20" s="46" t="s"/>
       <c r="O20" s="46" t="s"/>
@@ -7116,28 +7396,68 @@
         <v>1</v>
       </c>
       <c r="ER20" s="45">
-        <v>1</v>
-      </c>
-      <c r="ES20" s="44" t="s"/>
-      <c r="ET20" s="44" t="s"/>
-      <c r="EU20" s="44" t="s"/>
-      <c r="EV20" s="44" t="s"/>
-      <c r="EW20" s="44" t="s"/>
-      <c r="EX20" s="45" t="s"/>
-      <c r="EY20" s="45" t="s"/>
-      <c r="EZ20" s="45" t="s"/>
-      <c r="FA20" s="45" t="s"/>
-      <c r="FB20" s="45" t="s"/>
-      <c r="FC20" s="44" t="s"/>
-      <c r="FD20" s="44" t="s"/>
-      <c r="FE20" s="44" t="s"/>
-      <c r="FF20" s="44" t="s"/>
-      <c r="FG20" s="44" t="s"/>
-      <c r="FH20" s="45" t="s"/>
-      <c r="FI20" s="45" t="s"/>
-      <c r="FJ20" s="45" t="s"/>
-      <c r="FK20" s="45" t="s"/>
-      <c r="FL20" s="45" t="s"/>
+        <v>0</v>
+      </c>
+      <c r="ES20" s="44">
+        <v>23</v>
+      </c>
+      <c r="ET20" s="44">
+        <v>4</v>
+      </c>
+      <c r="EU20" s="44">
+        <v>1</v>
+      </c>
+      <c r="EV20" s="44">
+        <v>0</v>
+      </c>
+      <c r="EW20" s="44">
+        <v>0</v>
+      </c>
+      <c r="EX20" s="45">
+        <v>20</v>
+      </c>
+      <c r="EY20" s="45">
+        <v>1</v>
+      </c>
+      <c r="EZ20" s="45">
+        <v>0</v>
+      </c>
+      <c r="FA20" s="45">
+        <v>0</v>
+      </c>
+      <c r="FB20" s="45">
+        <v>0</v>
+      </c>
+      <c r="FC20" s="44">
+        <v>27</v>
+      </c>
+      <c r="FD20" s="44">
+        <v>3</v>
+      </c>
+      <c r="FE20" s="44">
+        <v>2</v>
+      </c>
+      <c r="FF20" s="44">
+        <v>2</v>
+      </c>
+      <c r="FG20" s="44">
+        <v>0</v>
+      </c>
+      <c r="FH20" s="45">
+        <v>30</v>
+      </c>
+      <c r="FI20" s="45">
+        <v>2</v>
+      </c>
+      <c r="FJ20" s="45">
+        <v>1</v>
+      </c>
+      <c r="FK20" s="45">
+        <v>1</v>
+      </c>
+      <c r="FL20" s="45">
+        <v>0</v>
+      </c>
     </row>
     <row r="21" spans="1:168">
       <c r="A21" s="37" t="s"/>
@@ -7832,35 +8152,35 @@
       <c r="E25" s="56" t="s"/>
       <c r="F25" s="58">
         <f>=SUM(F8:F24)</f>
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G25" s="58">
         <f>=SUM(G8:G23)</f>
-        <v>5250</v>
+        <v>5659</v>
       </c>
       <c r="H25" s="58">
         <f>=SUM(H8:H23)</f>
-        <v>665</v>
+        <v>748</v>
       </c>
       <c r="I25" s="58">
         <f>=SUM(I8:I23)</f>
-        <v>360</v>
+        <v>409</v>
       </c>
       <c r="J25" s="58">
         <f>=SUM(J8:J23)</f>
-        <v>155</v>
+        <v>181</v>
       </c>
       <c r="K25" s="58">
         <f>=SUM(K8:K23)</f>
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="L25" s="58">
         <f>=SUM(L8:L23)</f>
-        <v>210</v>
+        <v>160</v>
       </c>
       <c r="M25" s="59">
         <f>=K25/L25</f>
-        <v>0.285714285714286</v>
+        <v>0.45</v>
       </c>
       <c r="N25" s="58">
         <f>=SUM(N8:N24)</f>
@@ -8120,7 +8440,7 @@
       </c>
       <c r="BZ25" s="58">
         <f>=SUM(BZ8:BZ24)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CA25" s="44">
         <f>=SUM(CA8:CA24)</f>
@@ -8400,63 +8720,63 @@
       </c>
       <c r="ER25" s="58">
         <f>=SUM(ER8:ER24)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="ES25" s="44">
         <f>=SUM(ES8:ES24)</f>
-        <v>0</v>
+        <v>127</v>
       </c>
       <c r="ET25" s="44">
         <f>=SUM(ET8:ET24)</f>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="EU25" s="44">
         <f>=SUM(EU8:EU24)</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="EV25" s="44">
         <f>=SUM(EV8:EV24)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="EW25" s="44">
         <f>=SUM(EW8:EW24)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="EX25" s="58">
         <f>=SUM(EX8:EX24)</f>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="EY25" s="58">
         <f>=SUM(EY8:EY24)</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="EZ25" s="58">
         <f>=SUM(EZ8:EZ24)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="FA25" s="58">
         <f>=SUM(FA8:FA24)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="FB25" s="58">
         <f>=SUM(FB8:FB24)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="FC25" s="44">
         <f>=SUM(FC8:FC24)</f>
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="FD25" s="44">
         <f>=SUM(FD8:FD24)</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="FE25" s="44">
         <f>=SUM(FE8:FE24)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="FF25" s="44">
         <f>=SUM(FF8:FF24)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="FG25" s="44">
         <f>=SUM(FG8:FG24)</f>
@@ -8464,23 +8784,23 @@
       </c>
       <c r="FH25" s="58">
         <f>=SUM(FH8:FH24)</f>
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="FI25" s="58">
         <f>=SUM(FI8:FI24)</f>
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="FJ25" s="58">
         <f>=SUM(FJ8:FJ24)</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="FK25" s="58">
         <f>=SUM(FK8:FK24)</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="FL25" s="58">
         <f>=SUM(FL8:FL24)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
